--- a/docs/ZIPBODA_화면설계서_v0.1.xlsx
+++ b/docs/ZIPBODA_화면설계서_v0.1.xlsx
@@ -585,10 +585,24 @@
       <c r="F4" s="4" t="n"/>
     </row>
     <row r="5" ht="15.75" customHeight="1" s="19">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="4" t="n"/>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>사용자용/관리자용</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>청약 개편 — 평면도(2D/3D)를 청약 상세에 임베드하고 독립 평면도 메뉴(PLAN-01~04) 제거, 청약 신청 내부 위저드(SUBS-04~07)→외부 기관 사이트 링크 전환, 청약 상세(SUBS-03) 상세화, 평면도·3D 집구경 뷰어 신설(SUBS-08), 나의 청약(MY-01) 관심/구독/신청함 개편, 관리자 신청현황(ZB-A-SUBS-04) 제거</t>
+        </is>
+      </c>
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
     </row>
@@ -1640,7 +1654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="3.75" customWidth="1" style="19" min="1" max="1"/>
@@ -2009,7 +2023,7 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>(공통) 로고·통합검색바, 퀵메뉴(청약/평면도/가구/쇼룸/인테리어 영감/가점계산), 프로모션 배너, 마감임박 청약·인기 주택 구조·가구 특가 섹션 캐러셀.</t>
+          <t>(공통) 로고·통합검색바, 퀵메뉴(청약/가구/쇼룸/인테리어 영감/가점계산), 프로모션 배너, 마감임박 청약·인기 주택 구조·가구 특가 섹션 캐러셀.</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
@@ -2084,7 +2098,7 @@
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>(도출) 헤더 검색바로 주택/가구 통합 검색. 탭으로 청약·평면도·가구 결과 분리.</t>
+          <t>(도출) 헤더 검색바로 주택/가구 통합 검색. 탭으로 청약·가구 결과 분리.</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
@@ -2159,7 +2173,7 @@
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>(공통) '공공주택' 진행중 공고 목록. 지역(전체/서울/인천/경기)·공급기관(전체/LH/SH) 필터, 마감임박 뱃지(D-3), 평형 칩, 마감일·세대·경쟁률·입주 정보.</t>
+          <t>(공통) '공공주택' 진행중 공고 목록. 지역(전체/서울/인천/경기)·공급기관(전체/LH/SH/GH/IH) 필터, 마감임박 뱃지(D-3), 평형 칩, 마감일·세대·경쟁률·입주 정보.</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
@@ -2194,7 +2208,7 @@
       </c>
       <c r="M8" s="18" t="inlineStr">
         <is>
-          <t>지금 신청하기</t>
+          <t>상세 보기</t>
         </is>
       </c>
       <c r="N8" s="16" t="inlineStr">
@@ -2204,7 +2218,7 @@
       </c>
       <c r="O8" s="18" t="inlineStr">
         <is>
-          <t>카드 선택 시 청약 상세, CTA 시 신청 위저드</t>
+          <t>카드 선택 시 청약 상세</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2283,7 @@
       </c>
       <c r="M9" s="18" t="inlineStr">
         <is>
-          <t>지금 신청하기</t>
+          <t>상세 보기</t>
         </is>
       </c>
       <c r="N9" s="16" t="inlineStr">
@@ -2279,7 +2293,7 @@
       </c>
       <c r="O9" s="18" t="inlineStr">
         <is>
-          <t>핀/카드 선택 시 상세, CTA 시 신청 위저드</t>
+          <t>핀/카드 선택 시 상세</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2323,7 @@
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>(도출) 단지 개요·공급 유형·일정·경쟁률·평형별 정보와 연계된 평면도/3D, '이 스타일 쇼핑하기' 가구 추천.</t>
+          <t>(도출) 청약 타이틀·공사(LH/SH/GH/IH)·상태(접수예정/접수중/마감/취소)·D-day 헤더, 공고일·접수(시작~마감)일·공급유형·세대수·입주예정·경쟁률 정보 카드, 주소+지도, 평형별 정보 표, 평면도(2D)·3D 집구경 임베드 탭, 가구 추천. 실제 신청은 공급기관 사이트로 이동(집보다는 신청 대행 안 함).</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
@@ -2334,17 +2348,17 @@
       </c>
       <c r="K10" s="18" t="inlineStr">
         <is>
-          <t>상세 정보 영역, 정보 카드, 평면도 링크, 가구 추천</t>
+          <t>헤더(공사·상태 배지·D-day), 정보 카드, 지도, 평형 표, 평면도·3D 임베드 탭, 외부 신청 CTA·안내문, 가구 추천, 관심/구독/신청함 버튼</t>
         </is>
       </c>
       <c r="L10" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 버튼, 카드, 탭</t>
+          <t>텍스트, 배지, 카드, 지도, 탭, 3D 뷰어, 버튼</t>
         </is>
       </c>
       <c r="M10" s="18" t="inlineStr">
         <is>
-          <t>지금 신청하기</t>
+          <t>해당 기관에서 신청</t>
         </is>
       </c>
       <c r="N10" s="16" t="inlineStr">
@@ -2354,7 +2368,7 @@
       </c>
       <c r="O10" s="18" t="inlineStr">
         <is>
-          <t>신청 위저드 진입, 3D로 보기 시 뷰어</t>
+          <t>기관 신청 페이지(새 탭) 이동, 전체화면 집구경(ZB-U-SUBS-08) 진입, 관심/구독/신청함 표시</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2378,7 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>ZB-U-SUBS-04</t>
+          <t>ZB-U-SUBS-08</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -2374,27 +2388,27 @@
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>청약 신청 1단계 - 자격 확인</t>
+          <t>평면도·3D 집구경 뷰어</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>모달</t>
+          <t>상세</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>(공통) 신청 위저드 1/4. 무주택·거주지·소득 등 자격 요건 확인.</t>
+          <t>(공통) 청약 상세에서 진입하는 전체화면 뷰어. 2D 도면(방별 치수)과 3D 집구경(WebGL, 1인칭/3인칭)을 토글. 저사양·미지원 시 2D 폴백.</t>
         </is>
       </c>
       <c r="G11" s="17" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H11" s="16" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I11" s="16" t="inlineStr">
@@ -2409,17 +2423,17 @@
       </c>
       <c r="K11" s="18" t="inlineStr">
         <is>
-          <t>모달, 위저드(스텝), 입력 폼</t>
+          <t>2D 도면 뷰어, 3D WebGL 뷰어, 2D/3D·시점 토글, 정보 카드</t>
         </is>
       </c>
       <c r="L11" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 체크박스, 버튼</t>
+          <t>텍스트, 버튼, 토글, 3D 뷰어</t>
         </is>
       </c>
       <c r="M11" s="18" t="inlineStr">
         <is>
-          <t>다음</t>
+          <t>해당 기관에서 신청</t>
         </is>
       </c>
       <c r="N11" s="16" t="inlineStr">
@@ -2429,7 +2443,7 @@
       </c>
       <c r="O11" s="18" t="inlineStr">
         <is>
-          <t>다음 단계(평형 선택) 이동</t>
+          <t>시점 전환·회전 조작, 닫기 시 청약 상세 복귀, CTA 시 기관 신청 페이지(새 탭)</t>
         </is>
       </c>
     </row>
@@ -2439,32 +2453,32 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>ZB-U-SUBS-05</t>
+          <t>ZB-U-SCORE-01</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>청약</t>
+          <t>청약 가점</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>청약 신청 2단계 - 평형 선택</t>
+          <t>청약가점 계산기</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>모달</t>
+          <t>입력폼</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>(공통) 신청 위저드 2/4. 신청 평형·타입 선택.</t>
+          <t>(공통) 무주택 기간·부양가족 수·청약통장 기간 슬라이더로 총점(최고 84점) 계산, 등급/게이지, 가점 팁, '내 점수 저장하기', 결과 공유, 신청 가능 공고.</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H12" s="16" t="inlineStr">
@@ -2484,17 +2498,17 @@
       </c>
       <c r="K12" s="18" t="inlineStr">
         <is>
-          <t>모달, 위저드(스텝), 옵션 선택</t>
+          <t>총점 게이지, 슬라이더 카드, 팁 리스트, 저장 버튼</t>
         </is>
       </c>
       <c r="L12" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 라디오, 버튼</t>
+          <t>텍스트, 슬라이더, 카드, 버튼</t>
         </is>
       </c>
       <c r="M12" s="18" t="inlineStr">
         <is>
-          <t>다음</t>
+          <t>내 점수 저장하기</t>
         </is>
       </c>
       <c r="N12" s="16" t="inlineStr">
@@ -2504,7 +2518,7 @@
       </c>
       <c r="O12" s="18" t="inlineStr">
         <is>
-          <t>다음 단계(개인 정보) 이동</t>
+          <t>저장 시 마이페이지에 가점 기록</t>
         </is>
       </c>
     </row>
@@ -2514,37 +2528,37 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>ZB-U-SUBS-06</t>
+          <t>ZB-U-TOUR-01</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>청약</t>
+          <t>집구경</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>청약 신청 3단계 - 개인 정보</t>
+          <t>인테리어 영감 갤러리</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>모달</t>
+          <t>목록</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>(공통) 신청 위저드 3/4. 신청자 개인정보·연락처 입력 및 확인.</t>
+          <t>(공통) 공간 카테고리(전체/거실/침실/주방/다이닝/서재/욕실) 탭과 사용자 인테리어 사진 그리드(작성자·좋아요 수).</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H13" s="16" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I13" s="16" t="inlineStr">
@@ -2559,17 +2573,17 @@
       </c>
       <c r="K13" s="18" t="inlineStr">
         <is>
-          <t>모달, 위저드(스텝), 입력 폼</t>
+          <t>카테고리 탭, 이미지 카드 그리드</t>
         </is>
       </c>
       <c r="L13" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 입력 필드, 버튼</t>
+          <t>텍스트, 탭, 카드</t>
         </is>
       </c>
       <c r="M13" s="18" t="inlineStr">
         <is>
-          <t>신청하기</t>
+          <t>(없음)</t>
         </is>
       </c>
       <c r="N13" s="16" t="inlineStr">
@@ -2579,7 +2593,7 @@
       </c>
       <c r="O13" s="18" t="inlineStr">
         <is>
-          <t>신청 처리 후 완료 단계 이동</t>
+          <t>카드 선택 시 인테리어 상세</t>
         </is>
       </c>
     </row>
@@ -2589,17 +2603,17 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>ZB-U-SUBS-07</t>
+          <t>ZB-U-TOUR-02</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>청약</t>
+          <t>집구경</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>청약 신청 4단계 - 완료</t>
+          <t>인테리어 상세</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -2609,12 +2623,12 @@
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>(공통) '신청이 완료되었습니다!' 안내와 신청 내역 요약, 마이페이지 이동 안내.</t>
+          <t>(공통) 인테리어 사진 상세(작성자·좋아요)와 '이 스타일 쇼핑하기'로 사진 속 가구 쇼핑 유도.</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H14" s="16" t="inlineStr">
@@ -2634,17 +2648,17 @@
       </c>
       <c r="K14" s="18" t="inlineStr">
         <is>
-          <t>모달, 완료 안내, 요약 카드</t>
+          <t>모달, 이미지, 좋아요, 버튼</t>
         </is>
       </c>
       <c r="L14" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 버튼</t>
+          <t>텍스트, 버튼, 아이콘</t>
         </is>
       </c>
       <c r="M14" s="18" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>이 스타일 쇼핑하기</t>
         </is>
       </c>
       <c r="N14" s="16" t="inlineStr">
@@ -2654,7 +2668,7 @@
       </c>
       <c r="O14" s="18" t="inlineStr">
         <is>
-          <t>마이페이지 청약 신청 탭으로 이동</t>
+          <t>관련 가구 목록으로 이동</t>
         </is>
       </c>
     </row>
@@ -2664,27 +2678,27 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>ZB-U-SCORE-01</t>
+          <t>ZB-U-SHOW-01</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>청약 가점</t>
+          <t>쇼룸</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>청약가점 계산기</t>
+          <t>내 주변 쇼룸</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>입력폼</t>
+          <t>목록</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>(공통) 무주택 기간·부양가족 수·청약통장 기간 슬라이더로 총점(최고 84점) 계산, 등급/게이지, 가점 팁, '내 점수 저장하기', 결과 공유, 신청 가능 공고.</t>
+          <t>(공통) 지도 핀과 쇼룸 카드 리스트(영업 상태·거리·리뷰·'방문 예약'). 파트너 쇼룸(바움/폼/루네/벨라) 표시.</t>
         </is>
       </c>
       <c r="G15" s="17" t="inlineStr">
@@ -2694,7 +2708,7 @@
       </c>
       <c r="H15" s="16" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I15" s="16" t="inlineStr">
@@ -2709,17 +2723,17 @@
       </c>
       <c r="K15" s="18" t="inlineStr">
         <is>
-          <t>총점 게이지, 슬라이더 카드, 팁 리스트, 저장 버튼</t>
+          <t>지도(핀 마커), 쇼룸 카드 리스트, 상태 뱃지</t>
         </is>
       </c>
       <c r="L15" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 슬라이더, 카드, 버튼</t>
+          <t>텍스트, 지도, 버튼, 카드</t>
         </is>
       </c>
       <c r="M15" s="18" t="inlineStr">
         <is>
-          <t>내 점수 저장하기</t>
+          <t>방문 예약</t>
         </is>
       </c>
       <c r="N15" s="16" t="inlineStr">
@@ -2729,7 +2743,7 @@
       </c>
       <c r="O15" s="18" t="inlineStr">
         <is>
-          <t>저장 시 마이페이지에 가점 기록</t>
+          <t>카드/핀 선택 시 쇼룸 상세, CTA 시 예약</t>
         </is>
       </c>
     </row>
@@ -2739,27 +2753,27 @@
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>ZB-U-PLAN-01</t>
+          <t>ZB-U-SHOW-02</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>평면도</t>
+          <t>쇼룸</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>평면도 라이브러리</t>
+          <t>쇼룸 상세/방문 예약</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>상세</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>(공통) 평형(전체/39/59/84/114㎡)·방 개수·유형 필터로 보는 평면도 카드 목록. 2D/3D 뱃지, 평형·타입·구성 표시.</t>
+          <t>(도출) 쇼룸 상세 정보(주소·영업시간·전시 상품)와 방문 예약 폼(날짜·시간·인원).</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
@@ -2769,7 +2783,7 @@
       </c>
       <c r="H16" s="16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="I16" s="16" t="inlineStr">
@@ -2784,17 +2798,17 @@
       </c>
       <c r="K16" s="18" t="inlineStr">
         <is>
-          <t>필터 칩, 평면도 카드 그리드, 뱃지</t>
+          <t>상세 정보 영역, 예약 폼, 지도</t>
         </is>
       </c>
       <c r="L16" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 버튼(필터), 카드</t>
+          <t>텍스트, 입력 필드, 버튼</t>
         </is>
       </c>
       <c r="M16" s="18" t="inlineStr">
         <is>
-          <t>탐색하기</t>
+          <t>예약하기</t>
         </is>
       </c>
       <c r="N16" s="16" t="inlineStr">
@@ -2804,7 +2818,7 @@
       </c>
       <c r="O16" s="18" t="inlineStr">
         <is>
-          <t>카드 선택 시 평면도 뷰어 이동</t>
+          <t>예약 완료 시 마이페이지 예약 내역</t>
         </is>
       </c>
     </row>
@@ -2814,27 +2828,27 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>ZB-U-PLAN-02</t>
+          <t>ZB-U-COMM-01</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>평면도</t>
+          <t>커뮤니티</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>평면도 비교</t>
+          <t>커뮤니티 목록</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>현황</t>
+          <t>목록</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>(PC) 최대 3개 평면도를 나란히 비교하는 패널('2개 평면도 비교', 닫기 ✕).</t>
+          <t>(공통) 카테고리 칩(전체/인테리어/리뷰/가구/Q&amp;A/팁/비포·애프터), 인기글 히어로, 게시글 그리드, '+ 글쓰기'.</t>
         </is>
       </c>
       <c r="G17" s="17" t="inlineStr">
@@ -2859,17 +2873,17 @@
       </c>
       <c r="K17" s="18" t="inlineStr">
         <is>
-          <t>비교 패널, 평면도 뷰, 선택 카운터</t>
+          <t>카테고리 칩, 인기글 히어로, 게시글 그리드</t>
         </is>
       </c>
       <c r="L17" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 버튼, 카드</t>
+          <t>텍스트, 칩, 카드, 버튼</t>
         </is>
       </c>
       <c r="M17" s="18" t="inlineStr">
         <is>
-          <t>비교</t>
+          <t>+ 글쓰기</t>
         </is>
       </c>
       <c r="N17" s="16" t="inlineStr">
@@ -2879,7 +2893,7 @@
       </c>
       <c r="O17" s="18" t="inlineStr">
         <is>
-          <t>닫기 시 목록 복귀</t>
+          <t>게시글 선택 시 상세, 글쓰기 시 작성 화면</t>
         </is>
       </c>
     </row>
@@ -2889,17 +2903,17 @@
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>ZB-U-PLAN-03</t>
+          <t>ZB-U-COMM-02</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>평면도</t>
+          <t>커뮤니티</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>평면도 뷰어 - 2D</t>
+          <t>게시글 상세</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
@@ -2909,7 +2923,7 @@
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>(공통) 방별 치수가 표기된 인터랙티브 2D 도면과 매물 정보, '이 스타일 쇼핑하기' 가구 추천. 2D/3D 토글.</t>
+          <t>(도출) 게시글 본문·이미지, 좋아요·댓글 목록/작성.</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
@@ -2919,7 +2933,7 @@
       </c>
       <c r="H18" s="16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>CRUD</t>
         </is>
       </c>
       <c r="I18" s="16" t="inlineStr">
@@ -2934,17 +2948,17 @@
       </c>
       <c r="K18" s="18" t="inlineStr">
         <is>
-          <t>2D 도면 뷰어, 정보 카드, 가구 추천, 토글</t>
+          <t>상세 정보 영역, 댓글 목록, 입력창</t>
         </is>
       </c>
       <c r="L18" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 버튼, 토글, 카드</t>
+          <t>텍스트, 버튼, 리스트, 입력 필드</t>
         </is>
       </c>
       <c r="M18" s="18" t="inlineStr">
         <is>
-          <t>지금 신청하기</t>
+          <t>댓글 등록</t>
         </is>
       </c>
       <c r="N18" s="16" t="inlineStr">
@@ -2954,7 +2968,7 @@
       </c>
       <c r="O18" s="18" t="inlineStr">
         <is>
-          <t>3D 토글 시 3D 배치도, CTA 시 신청</t>
+          <t>댓글/좋아요 반영</t>
         </is>
       </c>
     </row>
@@ -2964,37 +2978,37 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>ZB-U-PLAN-04</t>
+          <t>ZB-U-COMM-03</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>평면도</t>
+          <t>커뮤니티</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>평면도 뷰어 - 3D 배치도(집구경)</t>
+          <t>글쓰기</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>상세</t>
+          <t>입력폼</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>(공통) WebGL 기반 3D 배치도. 1인칭/3인칭 시점 전환으로 내부 구조를 둘러봄. 매물 정보·가구 추천 연동.</t>
+          <t>(도출) 카테고리 선택·제목·본문·이미지 첨부로 커뮤니티 글 작성.</t>
         </is>
       </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="H19" s="16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="I19" s="16" t="inlineStr">
@@ -3009,17 +3023,17 @@
       </c>
       <c r="K19" s="18" t="inlineStr">
         <is>
-          <t>3D WebGL 뷰어, 시점 전환, 정보 카드</t>
+          <t>입력 폼, 이미지 업로드, 카테고리 선택</t>
         </is>
       </c>
       <c r="L19" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 버튼, 토글, 3D 뷰어</t>
+          <t>텍스트, 입력 필드, 드롭다운, 버튼</t>
         </is>
       </c>
       <c r="M19" s="18" t="inlineStr">
         <is>
-          <t>지금 신청하기</t>
+          <t>등록</t>
         </is>
       </c>
       <c r="N19" s="16" t="inlineStr">
@@ -3029,7 +3043,7 @@
       </c>
       <c r="O19" s="18" t="inlineStr">
         <is>
-          <t>시점 전환·회전 조작, CTA 시 신청</t>
+          <t>등록 완료 시 게시글 상세</t>
         </is>
       </c>
     </row>
@@ -3039,17 +3053,17 @@
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>ZB-U-TOUR-01</t>
+          <t>ZB-U-SHOP-01</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>집구경</t>
+          <t>장보기</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>인테리어 영감 갤러리</t>
+          <t>가구 쇼핑 목록</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
@@ -3059,7 +3073,7 @@
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>(공통) 공간 카테고리(전체/거실/침실/주방/다이닝/서재/욕실) 탭과 사용자 인테리어 사진 그리드(작성자·좋아요 수).</t>
+          <t>(공통·2차) 카테고리 탭/사이드바 필터(카테고리·할인율·정렬)로 보는 가구 상품 그리드. 할인율·브랜드·상품명·별점·가격·'+ 담기'.</t>
         </is>
       </c>
       <c r="G20" s="17" t="inlineStr">
@@ -3084,17 +3098,17 @@
       </c>
       <c r="K20" s="18" t="inlineStr">
         <is>
-          <t>카테고리 탭, 이미지 카드 그리드</t>
+          <t>카테고리 탭, 필터 사이드바, 상품 카드 그리드</t>
         </is>
       </c>
       <c r="L20" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 탭, 카드</t>
+          <t>텍스트, 버튼, 탭, 드롭다운, 카드</t>
         </is>
       </c>
       <c r="M20" s="18" t="inlineStr">
         <is>
-          <t>(없음)</t>
+          <t>+ 담기</t>
         </is>
       </c>
       <c r="N20" s="16" t="inlineStr">
@@ -3104,7 +3118,7 @@
       </c>
       <c r="O20" s="18" t="inlineStr">
         <is>
-          <t>카드 선택 시 인테리어 상세</t>
+          <t>담기 시 장바구니 추가, 카드 선택 시 상세</t>
         </is>
       </c>
     </row>
@@ -3114,27 +3128,27 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>ZB-U-TOUR-02</t>
+          <t>ZB-U-SHOP-02</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>집구경</t>
+          <t>장보기</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>인테리어 상세</t>
+          <t>상품 상세</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>모달</t>
+          <t>상세</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>(공통) 인테리어 사진 상세(작성자·좋아요)와 '이 스타일 쇼핑하기'로 사진 속 가구 쇼핑 유도.</t>
+          <t>(공통·2차) 이미지 갤러리, 색상·수량 선택, 상세정보·크기·리뷰 탭, '장바구니 담기 — {금액}'.</t>
         </is>
       </c>
       <c r="G21" s="17" t="inlineStr">
@@ -3159,17 +3173,17 @@
       </c>
       <c r="K21" s="18" t="inlineStr">
         <is>
-          <t>모달, 이미지, 좋아요, 버튼</t>
+          <t>상세 정보 영역, 이미지, 옵션 선택, 수량 스텝퍼, 리뷰</t>
         </is>
       </c>
       <c r="L21" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 버튼, 아이콘</t>
+          <t>텍스트, 버튼, 수량 스텝퍼, 탭, 리스트</t>
         </is>
       </c>
       <c r="M21" s="18" t="inlineStr">
         <is>
-          <t>이 스타일 쇼핑하기</t>
+          <t>장바구니 담기</t>
         </is>
       </c>
       <c r="N21" s="16" t="inlineStr">
@@ -3179,7 +3193,7 @@
       </c>
       <c r="O21" s="18" t="inlineStr">
         <is>
-          <t>관련 가구 목록으로 이동</t>
+          <t>담기 시 장바구니 모달 노출</t>
         </is>
       </c>
     </row>
@@ -3189,37 +3203,37 @@
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>ZB-U-SHOW-01</t>
+          <t>ZB-U-CART-01</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>쇼룸</t>
+          <t>장바구니</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>내 주변 쇼룸</t>
+          <t>장바구니</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>모달</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>(공통) 지도 핀과 쇼룸 카드 리스트(영업 상태·거리·리뷰·'방문 예약'). 파트너 쇼룸(바움/폼/루네/벨라) 표시.</t>
+          <t>(공통·2차) 담긴 상품 리스트·수량 조절·삭제, 합계, '결제하기 → {금액}'. 빈 상태 시 '쇼핑하기' 안내.</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="H22" s="16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>CRUD</t>
         </is>
       </c>
       <c r="I22" s="16" t="inlineStr">
@@ -3234,17 +3248,17 @@
       </c>
       <c r="K22" s="18" t="inlineStr">
         <is>
-          <t>지도(핀 마커), 쇼룸 카드 리스트, 상태 뱃지</t>
+          <t>모달/슬라이드오버, 상품 리스트, 수량 스텝퍼, 합계</t>
         </is>
       </c>
       <c r="L22" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 지도, 버튼, 카드</t>
+          <t>텍스트, 버튼, 수량 스텝퍼, 리스트</t>
         </is>
       </c>
       <c r="M22" s="18" t="inlineStr">
         <is>
-          <t>방문 예약</t>
+          <t>결제하기</t>
         </is>
       </c>
       <c r="N22" s="16" t="inlineStr">
@@ -3254,7 +3268,7 @@
       </c>
       <c r="O22" s="18" t="inlineStr">
         <is>
-          <t>카드/핀 선택 시 쇼룸 상세, CTA 시 예약</t>
+          <t>결제 플로우 이동, 빈 상태 시 쇼핑 이동</t>
         </is>
       </c>
     </row>
@@ -3264,32 +3278,32 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>ZB-U-SHOW-02</t>
+          <t>ZB-U-CART-02</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>쇼룸</t>
+          <t>장바구니</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>쇼룸 상세/방문 예약</t>
+          <t>결제</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>상세</t>
+          <t>입력폼</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>(도출) 쇼룸 상세 정보(주소·영업시간·전시 상품)와 방문 예약 폼(날짜·시간·인원).</t>
+          <t>(도출·2차) 배송지·결제수단 입력과 주문 요약, 결제 진행.</t>
         </is>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="H23" s="16" t="inlineStr">
@@ -3309,17 +3323,17 @@
       </c>
       <c r="K23" s="18" t="inlineStr">
         <is>
-          <t>상세 정보 영역, 예약 폼, 지도</t>
+          <t>입력 폼, 주문 요약, 결제수단 선택</t>
         </is>
       </c>
       <c r="L23" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 입력 필드, 버튼</t>
+          <t>텍스트, 입력 필드, 라디오, 버튼</t>
         </is>
       </c>
       <c r="M23" s="18" t="inlineStr">
         <is>
-          <t>예약하기</t>
+          <t>결제하기</t>
         </is>
       </c>
       <c r="N23" s="16" t="inlineStr">
@@ -3329,7 +3343,7 @@
       </c>
       <c r="O23" s="18" t="inlineStr">
         <is>
-          <t>예약 완료 시 마이페이지 예약 내역</t>
+          <t>결제 완료 시 주문완료/주문내역</t>
         </is>
       </c>
     </row>
@@ -3339,39 +3353,39 @@
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>ZB-U-COMM-01</t>
+          <t>ZB-U-CART-03</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>커뮤니티</t>
+          <t>장바구니</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>커뮤니티 목록</t>
+          <t>주문 완료</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>콘텐츠</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>(공통) 카테고리 칩(전체/인테리어/리뷰/가구/Q&amp;A/팁/비포·애프터), 인기글 히어로, 게시글 그리드, '+ 글쓰기'.</t>
+          <t>(도출·2차) 주문 완료 안내와 주문 번호·배송 예정, 주문내역 이동.</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="H24" s="16" t="inlineStr">
+        <is>
           <t>R</t>
         </is>
       </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
       <c r="I24" s="16" t="inlineStr">
         <is>
           <t>✕</t>
@@ -3384,17 +3398,17 @@
       </c>
       <c r="K24" s="18" t="inlineStr">
         <is>
-          <t>카테고리 칩, 인기글 히어로, 게시글 그리드</t>
+          <t>완료 안내, 주문 요약 카드</t>
         </is>
       </c>
       <c r="L24" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 칩, 카드, 버튼</t>
+          <t>텍스트, 버튼</t>
         </is>
       </c>
       <c r="M24" s="18" t="inlineStr">
         <is>
-          <t>+ 글쓰기</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="N24" s="16" t="inlineStr">
@@ -3404,7 +3418,7 @@
       </c>
       <c r="O24" s="18" t="inlineStr">
         <is>
-          <t>게시글 선택 시 상세, 글쓰기 시 작성 화면</t>
+          <t>마이페이지 주문내역 이동</t>
         </is>
       </c>
     </row>
@@ -3414,37 +3428,37 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>ZB-U-COMM-02</t>
+          <t>ZB-U-MY-01</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>커뮤니티</t>
+          <t>마이페이지</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>게시글 상세</t>
+          <t>나의 청약</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>상세</t>
+          <t>현황</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>(도출) 게시글 본문·이미지, 좋아요·댓글 목록/작성.</t>
+          <t>(공통) 프로필(인증 상태)·통계와 관심/구독 공고 목록(단지·상태·D-day). 각 공고에서 기관 신청 바로가기와 '신청함' 자가표시 관리.</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="H25" s="16" t="inlineStr">
         <is>
-          <t>CRUD</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="I25" s="16" t="inlineStr">
@@ -3459,17 +3473,17 @@
       </c>
       <c r="K25" s="18" t="inlineStr">
         <is>
-          <t>상세 정보 영역, 댓글 목록, 입력창</t>
+          <t>프로필 카드, 통계 카드, 탭, 관심/구독 공고 리스트(상태·D-day), 신청 바로가기, 신청함 토글</t>
         </is>
       </c>
       <c r="L25" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 버튼, 리스트, 입력 필드</t>
+          <t>텍스트, 버튼, 탭, 카드</t>
         </is>
       </c>
       <c r="M25" s="18" t="inlineStr">
         <is>
-          <t>댓글 등록</t>
+          <t>(없음)</t>
         </is>
       </c>
       <c r="N25" s="16" t="inlineStr">
@@ -3479,7 +3493,7 @@
       </c>
       <c r="O25" s="18" t="inlineStr">
         <is>
-          <t>댓글/좋아요 반영</t>
+          <t>항목 선택 시 청약 상세, 신청 바로가기 시 기관 페이지(새 탭)</t>
         </is>
       </c>
     </row>
@@ -3489,27 +3503,27 @@
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>ZB-U-COMM-03</t>
+          <t>ZB-U-MY-02</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>커뮤니티</t>
+          <t>마이페이지</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>글쓰기</t>
+          <t>찜 목록</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>입력폼</t>
+          <t>목록</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>(도출) 카테고리 선택·제목·본문·이미지 첨부로 커뮤니티 글 작성.</t>
+          <t>(공통·2차) 찜한 가구 목록(브랜드·상품명·가격)과 '구매'·'삭제'.</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr">
@@ -3519,7 +3533,7 @@
       </c>
       <c r="H26" s="16" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>CRUD</t>
         </is>
       </c>
       <c r="I26" s="16" t="inlineStr">
@@ -3534,17 +3548,17 @@
       </c>
       <c r="K26" s="18" t="inlineStr">
         <is>
-          <t>입력 폼, 이미지 업로드, 카테고리 선택</t>
+          <t>탭, 찜 상품 리스트</t>
         </is>
       </c>
       <c r="L26" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 입력 필드, 드롭다운, 버튼</t>
+          <t>텍스트, 버튼, 탭, 카드</t>
         </is>
       </c>
       <c r="M26" s="18" t="inlineStr">
         <is>
-          <t>등록</t>
+          <t>구매</t>
         </is>
       </c>
       <c r="N26" s="16" t="inlineStr">
@@ -3554,7 +3568,7 @@
       </c>
       <c r="O26" s="18" t="inlineStr">
         <is>
-          <t>등록 완료 시 게시글 상세</t>
+          <t>구매 시 결제/상품, 삭제 시 찜 해제</t>
         </is>
       </c>
     </row>
@@ -3564,39 +3578,39 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>ZB-U-SHOP-01</t>
+          <t>ZB-U-MY-03</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>장보기</t>
+          <t>마이페이지</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>가구 쇼핑 목록</t>
+          <t>주문내역</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>현황</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>(공통·2차) 카테고리 탭/사이드바 필터(카테고리·할인율·정렬)로 보는 가구 상품 그리드. 할인율·브랜드·상품명·별점·가격·'+ 담기'.</t>
+          <t>(공통·2차) 주문 목록과 배송 상태 뱃지(배송완료/배송중/준비중).</t>
         </is>
       </c>
       <c r="G27" s="17" t="inlineStr">
         <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="H27" s="16" t="inlineStr">
+        <is>
           <t>R</t>
         </is>
       </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
       <c r="I27" s="16" t="inlineStr">
         <is>
           <t>✕</t>
@@ -3609,17 +3623,17 @@
       </c>
       <c r="K27" s="18" t="inlineStr">
         <is>
-          <t>카테고리 탭, 필터 사이드바, 상품 카드 그리드</t>
+          <t>탭, 주문 리스트(상태 뱃지)</t>
         </is>
       </c>
       <c r="L27" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 버튼, 탭, 드롭다운, 카드</t>
+          <t>텍스트, 상태 뱃지, 탭, 카드</t>
         </is>
       </c>
       <c r="M27" s="18" t="inlineStr">
         <is>
-          <t>+ 담기</t>
+          <t>(없음)</t>
         </is>
       </c>
       <c r="N27" s="16" t="inlineStr">
@@ -3629,7 +3643,7 @@
       </c>
       <c r="O27" s="18" t="inlineStr">
         <is>
-          <t>담기 시 장바구니 추가, 카드 선택 시 상세</t>
+          <t>주문 선택 시 주문/배송 상세</t>
         </is>
       </c>
     </row>
@@ -3639,37 +3653,37 @@
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>ZB-U-SHOP-02</t>
+          <t>ZB-U-MY-04</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>장보기</t>
+          <t>마이페이지</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>상품 상세</t>
+          <t>프로필 수정</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>상세</t>
+          <t>입력폼</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>(공통·2차) 이미지 갤러리, 색상·수량 선택, 상세정보·크기·리뷰 탭, '장바구니 담기 — {금액}'.</t>
+          <t>(도출) 프로필(이름·연락처·본인인증)·비밀번호·알림 설정 수정.</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="H28" s="16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="I28" s="16" t="inlineStr">
@@ -3684,17 +3698,17 @@
       </c>
       <c r="K28" s="18" t="inlineStr">
         <is>
-          <t>상세 정보 영역, 이미지, 옵션 선택, 수량 스텝퍼, 리뷰</t>
+          <t>입력 폼, 본인인증, 토글</t>
         </is>
       </c>
       <c r="L28" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 버튼, 수량 스텝퍼, 탭, 리스트</t>
+          <t>텍스트, 입력 필드, 토글, 버튼</t>
         </is>
       </c>
       <c r="M28" s="18" t="inlineStr">
         <is>
-          <t>장바구니 담기</t>
+          <t>저장</t>
         </is>
       </c>
       <c r="N28" s="16" t="inlineStr">
@@ -3704,7 +3718,7 @@
       </c>
       <c r="O28" s="18" t="inlineStr">
         <is>
-          <t>담기 시 장바구니 모달 노출</t>
+          <t>저장 시 마이페이지 복귀</t>
         </is>
       </c>
     </row>
@@ -3714,37 +3728,37 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>ZB-U-CART-01</t>
+          <t>ZB-U-COM-01</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>장바구니</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>장바구니</t>
+          <t>공통 헤더/GNB</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>모달</t>
+          <t>콘텐츠</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>(공통·2차) 담긴 상품 리스트·수량 조절·삭제, 합계, '결제하기 → {금액}'. 빈 상태 시 '쇼핑하기' 안내.</t>
+          <t>(공통) 로고·통합검색바·주요 메뉴/알림·프로필. 로그인 상태에 따라 표시 분기.</t>
         </is>
       </c>
       <c r="G29" s="17" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H29" s="16" t="inlineStr">
         <is>
-          <t>CRUD</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I29" s="16" t="inlineStr">
@@ -3759,27 +3773,27 @@
       </c>
       <c r="K29" s="18" t="inlineStr">
         <is>
-          <t>모달/슬라이드오버, 상품 리스트, 수량 스텝퍼, 합계</t>
+          <t>헤더, 검색바, 메뉴, 알림 아이콘</t>
         </is>
       </c>
       <c r="L29" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 버튼, 수량 스텝퍼, 리스트</t>
+          <t>텍스트, 검색바, 버튼, 아이콘</t>
         </is>
       </c>
       <c r="M29" s="18" t="inlineStr">
         <is>
-          <t>결제하기</t>
+          <t>(없음)</t>
         </is>
       </c>
       <c r="N29" s="16" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O29" s="18" t="inlineStr">
         <is>
-          <t>결제 플로우 이동, 빈 상태 시 쇼핑 이동</t>
+          <t>메뉴 선택 시 라우팅</t>
         </is>
       </c>
     </row>
@@ -3789,37 +3803,37 @@
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>ZB-U-CART-02</t>
+          <t>ZB-U-COM-02</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>장바구니</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>결제</t>
+          <t>하단 탭 내비게이션</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>입력폼</t>
+          <t>콘텐츠</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>(도출·2차) 배송지·결제수단 입력과 주문 요약, 결제 진행.</t>
+          <t>(Mobile) 홈/쇼핑/커뮤니티/쇼룸/마이페이지 5탭 내비.</t>
         </is>
       </c>
       <c r="G30" s="17" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H30" s="16" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I30" s="16" t="inlineStr">
@@ -3834,27 +3848,27 @@
       </c>
       <c r="K30" s="18" t="inlineStr">
         <is>
-          <t>입력 폼, 주문 요약, 결제수단 선택</t>
+          <t>하단 탭 내비게이션</t>
         </is>
       </c>
       <c r="L30" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 입력 필드, 라디오, 버튼</t>
+          <t>탭, 아이콘</t>
         </is>
       </c>
       <c r="M30" s="18" t="inlineStr">
         <is>
-          <t>결제하기</t>
+          <t>(없음)</t>
         </is>
       </c>
       <c r="N30" s="16" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O30" s="18" t="inlineStr">
         <is>
-          <t>결제 완료 시 주문완료/주문내역</t>
+          <t>탭 선택 시 각 페이지 라우팅</t>
         </is>
       </c>
     </row>
@@ -3864,17 +3878,17 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>ZB-U-CART-03</t>
+          <t>ZB-U-COM-03</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>장바구니</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>주문 완료</t>
+          <t>푸터</t>
         </is>
       </c>
       <c r="E31" s="14" t="inlineStr">
@@ -3884,12 +3898,12 @@
       </c>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>(도출·2차) 주문 완료 안내와 주문 번호·배송 예정, 주문내역 이동.</t>
+          <t>(PC) 서비스 소개·약관·고객센터·회사 정보 푸터.</t>
         </is>
       </c>
       <c r="G31" s="17" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H31" s="16" t="inlineStr">
@@ -3909,27 +3923,27 @@
       </c>
       <c r="K31" s="18" t="inlineStr">
         <is>
-          <t>완료 안내, 주문 요약 카드</t>
+          <t>푸터</t>
         </is>
       </c>
       <c r="L31" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 버튼</t>
+          <t>텍스트, 링크</t>
         </is>
       </c>
       <c r="M31" s="18" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>(없음)</t>
         </is>
       </c>
       <c r="N31" s="16" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O31" s="18" t="inlineStr">
         <is>
-          <t>마이페이지 주문내역 이동</t>
+          <t>링크 선택 시 정책/안내 이동</t>
         </is>
       </c>
     </row>
@@ -3939,37 +3953,37 @@
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>ZB-U-MY-01</t>
+          <t>ZB-U-COM-04</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>마이페이지</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>나의 청약</t>
+          <t>비로그인 헤더</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>현황</t>
+          <t>콘텐츠</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>(공통) 프로필(인증 상태)·통계(신청완료/저장됨/주문/리뷰)와 청약 신청 목록(단지·평형·상태·D-day).</t>
+          <t>(공통) 미로그인 상태 헤더(로고·검색·'로그인').</t>
         </is>
       </c>
       <c r="G32" s="17" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H32" s="16" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="I32" s="16" t="inlineStr">
@@ -3984,27 +3998,27 @@
       </c>
       <c r="K32" s="18" t="inlineStr">
         <is>
-          <t>프로필 카드, 통계 카드, 탭, 청약 현황 리스트</t>
+          <t>헤더, 검색바, 버튼</t>
         </is>
       </c>
       <c r="L32" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 버튼, 탭, 카드</t>
+          <t>텍스트, 검색바, 버튼</t>
         </is>
       </c>
       <c r="M32" s="18" t="inlineStr">
         <is>
-          <t>(없음)</t>
+          <t>로그인</t>
         </is>
       </c>
       <c r="N32" s="16" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="O32" s="18" t="inlineStr">
         <is>
-          <t>항목 선택 시 청약/평면도 상세, 수정 시 프로필 수정</t>
+          <t>'로그인' 시 로그인 화면</t>
         </is>
       </c>
     </row>
@@ -4014,27 +4028,27 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>ZB-U-MY-02</t>
+          <t>ZB-U-COM-05</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>마이페이지</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>찜 목록</t>
+          <t>알림 패널</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>모달</t>
         </is>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>(공통·2차) 찜한 가구 목록(브랜드·상품명·가격)과 '구매'·'삭제'.</t>
+          <t>(공통) 마감임박·구독·주문 알림을 모아 보는 패널.</t>
         </is>
       </c>
       <c r="G33" s="17" t="inlineStr">
@@ -4044,7 +4058,7 @@
       </c>
       <c r="H33" s="16" t="inlineStr">
         <is>
-          <t>CRUD</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I33" s="16" t="inlineStr">
@@ -4059,17 +4073,17 @@
       </c>
       <c r="K33" s="18" t="inlineStr">
         <is>
-          <t>탭, 찜 상품 리스트</t>
+          <t>알림 패널, 알림 리스트</t>
         </is>
       </c>
       <c r="L33" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 버튼, 탭, 카드</t>
+          <t>텍스트, 리스트, 버튼</t>
         </is>
       </c>
       <c r="M33" s="18" t="inlineStr">
         <is>
-          <t>구매</t>
+          <t>(없음)</t>
         </is>
       </c>
       <c r="N33" s="16" t="inlineStr">
@@ -4079,535 +4093,17 @@
       </c>
       <c r="O33" s="18" t="inlineStr">
         <is>
-          <t>구매 시 결제/상품, 삭제 시 찜 해제</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" s="19">
-      <c r="A34" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>ZB-U-MY-03</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>마이페이지</t>
-        </is>
-      </c>
-      <c r="D34" s="15" t="inlineStr">
-        <is>
-          <t>주문내역</t>
-        </is>
-      </c>
-      <c r="E34" s="14" t="inlineStr">
-        <is>
-          <t>현황</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="inlineStr">
-        <is>
-          <t>(공통·2차) 주문 목록과 배송 상태 뱃지(배송완료/배송중/준비중).</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="H34" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="J34" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="K34" s="18" t="inlineStr">
-        <is>
-          <t>탭, 주문 리스트(상태 뱃지)</t>
-        </is>
-      </c>
-      <c r="L34" s="18" t="inlineStr">
-        <is>
-          <t>텍스트, 상태 뱃지, 탭, 카드</t>
-        </is>
-      </c>
-      <c r="M34" s="18" t="inlineStr">
-        <is>
-          <t>(없음)</t>
-        </is>
-      </c>
-      <c r="N34" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O34" s="18" t="inlineStr">
-        <is>
-          <t>주문 선택 시 주문/배송 상세</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" s="19">
-      <c r="A35" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>ZB-U-MY-04</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>마이페이지</t>
-        </is>
-      </c>
-      <c r="D35" s="15" t="inlineStr">
-        <is>
-          <t>프로필 수정</t>
-        </is>
-      </c>
-      <c r="E35" s="14" t="inlineStr">
-        <is>
-          <t>입력폼</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="inlineStr">
-        <is>
-          <t>(도출) 프로필(이름·연락처·본인인증)·비밀번호·알림 설정 수정.</t>
-        </is>
-      </c>
-      <c r="G35" s="17" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="H35" s="16" t="inlineStr">
-        <is>
-          <t>CRU</t>
-        </is>
-      </c>
-      <c r="I35" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="J35" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="K35" s="18" t="inlineStr">
-        <is>
-          <t>입력 폼, 본인인증, 토글</t>
-        </is>
-      </c>
-      <c r="L35" s="18" t="inlineStr">
-        <is>
-          <t>텍스트, 입력 필드, 토글, 버튼</t>
-        </is>
-      </c>
-      <c r="M35" s="18" t="inlineStr">
-        <is>
-          <t>저장</t>
-        </is>
-      </c>
-      <c r="N35" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O35" s="18" t="inlineStr">
-        <is>
-          <t>저장 시 마이페이지 복귀</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" s="19">
-      <c r="A36" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>ZB-U-COM-01</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="D36" s="15" t="inlineStr">
-        <is>
-          <t>공통 헤더/GNB</t>
-        </is>
-      </c>
-      <c r="E36" s="14" t="inlineStr">
-        <is>
-          <t>콘텐츠</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="inlineStr">
-        <is>
-          <t>(공통) 로고·통합검색바·주요 메뉴/알림·프로필. 로그인 상태에 따라 표시 분기.</t>
-        </is>
-      </c>
-      <c r="G36" s="17" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H36" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I36" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="J36" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="K36" s="18" t="inlineStr">
-        <is>
-          <t>헤더, 검색바, 메뉴, 알림 아이콘</t>
-        </is>
-      </c>
-      <c r="L36" s="18" t="inlineStr">
-        <is>
-          <t>텍스트, 검색바, 버튼, 아이콘</t>
-        </is>
-      </c>
-      <c r="M36" s="18" t="inlineStr">
-        <is>
-          <t>(없음)</t>
-        </is>
-      </c>
-      <c r="N36" s="16" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O36" s="18" t="inlineStr">
-        <is>
-          <t>메뉴 선택 시 라우팅</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" s="19">
-      <c r="A37" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>ZB-U-COM-02</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="D37" s="15" t="inlineStr">
-        <is>
-          <t>하단 탭 내비게이션</t>
-        </is>
-      </c>
-      <c r="E37" s="14" t="inlineStr">
-        <is>
-          <t>콘텐츠</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="inlineStr">
-        <is>
-          <t>(Mobile) 홈/쇼핑/커뮤니티/쇼룸/마이페이지 5탭 내비.</t>
-        </is>
-      </c>
-      <c r="G37" s="17" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H37" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I37" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="J37" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="K37" s="18" t="inlineStr">
-        <is>
-          <t>하단 탭 내비게이션</t>
-        </is>
-      </c>
-      <c r="L37" s="18" t="inlineStr">
-        <is>
-          <t>탭, 아이콘</t>
-        </is>
-      </c>
-      <c r="M37" s="18" t="inlineStr">
-        <is>
-          <t>(없음)</t>
-        </is>
-      </c>
-      <c r="N37" s="16" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O37" s="18" t="inlineStr">
-        <is>
-          <t>탭 선택 시 각 페이지 라우팅</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" s="19">
-      <c r="A38" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" s="14" t="inlineStr">
-        <is>
-          <t>ZB-U-COM-03</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="D38" s="15" t="inlineStr">
-        <is>
-          <t>푸터</t>
-        </is>
-      </c>
-      <c r="E38" s="14" t="inlineStr">
-        <is>
-          <t>콘텐츠</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="inlineStr">
-        <is>
-          <t>(PC) 서비스 소개·약관·고객센터·회사 정보 푸터.</t>
-        </is>
-      </c>
-      <c r="G38" s="17" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H38" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I38" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="J38" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="K38" s="18" t="inlineStr">
-        <is>
-          <t>푸터</t>
-        </is>
-      </c>
-      <c r="L38" s="18" t="inlineStr">
-        <is>
-          <t>텍스트, 링크</t>
-        </is>
-      </c>
-      <c r="M38" s="18" t="inlineStr">
-        <is>
-          <t>(없음)</t>
-        </is>
-      </c>
-      <c r="N38" s="16" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O38" s="18" t="inlineStr">
-        <is>
-          <t>링크 선택 시 정책/안내 이동</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" s="19">
-      <c r="A39" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" s="14" t="inlineStr">
-        <is>
-          <t>ZB-U-COM-04</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="D39" s="15" t="inlineStr">
-        <is>
-          <t>비로그인 헤더</t>
-        </is>
-      </c>
-      <c r="E39" s="14" t="inlineStr">
-        <is>
-          <t>콘텐츠</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="inlineStr">
-        <is>
-          <t>(공통) 미로그인 상태 헤더(로고·검색·'로그인').</t>
-        </is>
-      </c>
-      <c r="G39" s="17" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H39" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="I39" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="J39" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="K39" s="18" t="inlineStr">
-        <is>
-          <t>헤더, 검색바, 버튼</t>
-        </is>
-      </c>
-      <c r="L39" s="18" t="inlineStr">
-        <is>
-          <t>텍스트, 검색바, 버튼</t>
-        </is>
-      </c>
-      <c r="M39" s="18" t="inlineStr">
-        <is>
-          <t>로그인</t>
-        </is>
-      </c>
-      <c r="N39" s="16" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O39" s="18" t="inlineStr">
-        <is>
-          <t>'로그인' 시 로그인 화면</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" s="19">
-      <c r="A40" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="B40" s="14" t="inlineStr">
-        <is>
-          <t>ZB-U-COM-05</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="D40" s="15" t="inlineStr">
-        <is>
-          <t>알림 패널</t>
-        </is>
-      </c>
-      <c r="E40" s="14" t="inlineStr">
-        <is>
-          <t>모달</t>
-        </is>
-      </c>
-      <c r="F40" s="14" t="inlineStr">
-        <is>
-          <t>(공통) 마감임박·구독·주문 알림을 모아 보는 패널.</t>
-        </is>
-      </c>
-      <c r="G40" s="17" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="H40" s="16" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="I40" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="K40" s="18" t="inlineStr">
-        <is>
-          <t>알림 패널, 알림 리스트</t>
-        </is>
-      </c>
-      <c r="L40" s="18" t="inlineStr">
-        <is>
-          <t>텍스트, 리스트, 버튼</t>
-        </is>
-      </c>
-      <c r="M40" s="18" t="inlineStr">
-        <is>
-          <t>(없음)</t>
-        </is>
-      </c>
-      <c r="N40" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O40" s="18" t="inlineStr">
-        <is>
           <t>알림 선택 시 관련 화면 이동</t>
         </is>
       </c>
     </row>
+    <row r="34" s="19"/>
+    <row r="35" s="19"/>
+    <row r="36" s="19"/>
+    <row r="37" s="19"/>
+    <row r="38" s="19"/>
+    <row r="39" s="19"/>
+    <row r="40" s="19"/>
     <row r="41" ht="15.75" customHeight="1" s="19"/>
     <row r="42" ht="15.75" customHeight="1" s="19"/>
     <row r="43" ht="15.75" customHeight="1" s="19"/>
@@ -5554,7 +5050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="3.75" customWidth="1" style="19" min="1" max="1"/>
@@ -6053,17 +5549,17 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>ZB-A-SUBS-04</t>
+          <t>ZB-A-PLAN-01</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>청약 관리</t>
+          <t>자산 관리</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>청약 신청 현황 관리</t>
+          <t>평면도/3D 자산 목록</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -6073,7 +5569,7 @@
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>(도출) 사용자 청약 신청 내역을 조회·상태 관리·통계 확인.</t>
+          <t>(도출) 평면도(2D)·3D 배치도 자산을 단지/평형별로 관리. (공고 연계)</t>
         </is>
       </c>
       <c r="G8" s="16" t="inlineStr">
@@ -6088,7 +5584,7 @@
       </c>
       <c r="I8" s="17" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>CRU</t>
         </is>
       </c>
       <c r="J8" s="16" t="inlineStr">
@@ -6098,7 +5594,7 @@
       </c>
       <c r="K8" s="18" t="inlineStr">
         <is>
-          <t>목록 테이블, 필터, 상태 변경</t>
+          <t>목록 테이블, 미리보기, 필터</t>
         </is>
       </c>
       <c r="L8" s="18" t="inlineStr">
@@ -6118,7 +5614,7 @@
       </c>
       <c r="O8" s="18" t="inlineStr">
         <is>
-          <t>행 선택 시 신청 상세</t>
+          <t>행 선택 시 자산 상세/수정</t>
         </is>
       </c>
     </row>
@@ -6128,7 +5624,7 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>ZB-A-PLAN-01</t>
+          <t>ZB-A-PLAN-02</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -6138,17 +5634,17 @@
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>평면도/3D 자산 목록</t>
+          <t>평면도/3D 자산 등록</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>입력폼</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>(도출) 평면도(2D)·3D 배치도 자산을 단지/평형별로 관리.</t>
+          <t>(도출) 평면도 이미지·치수·3D(WebGL) 모델/씬 파일 업로드와 매핑. (공고 연계)</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
@@ -6173,17 +5669,17 @@
       </c>
       <c r="K9" s="18" t="inlineStr">
         <is>
-          <t>목록 테이블, 미리보기, 필터</t>
+          <t>입력 폼, 파일 업로드, 3D 미리보기</t>
         </is>
       </c>
       <c r="L9" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 테이블, 버튼</t>
+          <t>텍스트, 파일 업로드, 버튼</t>
         </is>
       </c>
       <c r="M9" s="18" t="inlineStr">
         <is>
-          <t>(없음)</t>
+          <t>저장</t>
         </is>
       </c>
       <c r="N9" s="16" t="inlineStr">
@@ -6193,7 +5689,7 @@
       </c>
       <c r="O9" s="18" t="inlineStr">
         <is>
-          <t>행 선택 시 자산 상세/수정</t>
+          <t>저장 시 자산 목록 복귀</t>
         </is>
       </c>
     </row>
@@ -6203,27 +5699,27 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>ZB-A-PLAN-02</t>
+          <t>ZB-A-TOUR-01</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>자산 관리</t>
+          <t>콘텐츠 관리</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>평면도/3D 자산 등록</t>
+          <t>인테리어 영감 관리</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>입력폼</t>
+          <t>목록</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>(도출) 평면도 이미지·치수·3D(WebGL) 모델/씬 파일 업로드와 매핑.</t>
+          <t>(도출) 인테리어 영감 콘텐츠 등록·노출·카테고리·상품 태깅 관리.</t>
         </is>
       </c>
       <c r="G10" s="16" t="inlineStr">
@@ -6238,7 +5734,7 @@
       </c>
       <c r="I10" s="17" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>CRUD</t>
         </is>
       </c>
       <c r="J10" s="16" t="inlineStr">
@@ -6248,17 +5744,17 @@
       </c>
       <c r="K10" s="18" t="inlineStr">
         <is>
-          <t>입력 폼, 파일 업로드, 3D 미리보기</t>
+          <t>목록 테이블, 이미지 업로드, 태깅</t>
         </is>
       </c>
       <c r="L10" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 파일 업로드, 버튼</t>
+          <t>텍스트, 테이블, 파일 업로드, 버튼</t>
         </is>
       </c>
       <c r="M10" s="18" t="inlineStr">
         <is>
-          <t>저장</t>
+          <t>(없음)</t>
         </is>
       </c>
       <c r="N10" s="16" t="inlineStr">
@@ -6268,7 +5764,7 @@
       </c>
       <c r="O10" s="18" t="inlineStr">
         <is>
-          <t>저장 시 자산 목록 복귀</t>
+          <t>행 선택 시 콘텐츠 상세/수정</t>
         </is>
       </c>
     </row>
@@ -6278,17 +5774,17 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>ZB-A-TOUR-01</t>
+          <t>ZB-A-SHOW-01</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>콘텐츠 관리</t>
+          <t>파트너 관리</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>인테리어 영감 관리</t>
+          <t>쇼룸/파트너 관리</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -6298,7 +5794,7 @@
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>(도출) 인테리어 영감 콘텐츠 등록·노출·카테고리·상품 태깅 관리.</t>
+          <t>(도출) 파트너 쇼룸 정보·위치·전시 상품·예약 슬롯 관리.</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
@@ -6323,12 +5819,12 @@
       </c>
       <c r="K11" s="18" t="inlineStr">
         <is>
-          <t>목록 테이블, 이미지 업로드, 태깅</t>
+          <t>목록 테이블, 지도, 입력 폼</t>
         </is>
       </c>
       <c r="L11" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 테이블, 파일 업로드, 버튼</t>
+          <t>텍스트, 테이블, 지도, 버튼</t>
         </is>
       </c>
       <c r="M11" s="18" t="inlineStr">
@@ -6343,7 +5839,7 @@
       </c>
       <c r="O11" s="18" t="inlineStr">
         <is>
-          <t>행 선택 시 콘텐츠 상세/수정</t>
+          <t>행 선택 시 쇼룸 상세/수정</t>
         </is>
       </c>
     </row>
@@ -6353,17 +5849,17 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>ZB-A-SHOW-01</t>
+          <t>ZB-A-SHOP-01</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>파트너 관리</t>
+          <t>상품 관리</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>쇼룸/파트너 관리</t>
+          <t>상품 관리(2차)</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -6373,7 +5869,7 @@
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>(도출) 파트너 쇼룸 정보·위치·전시 상품·예약 슬롯 관리.</t>
+          <t>(도출·2차) 가구 상품 등록·수정·재고·가격·노출 관리.</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
@@ -6398,12 +5894,12 @@
       </c>
       <c r="K12" s="18" t="inlineStr">
         <is>
-          <t>목록 테이블, 지도, 입력 폼</t>
+          <t>목록 테이블, 입력 폼, 이미지 업로드</t>
         </is>
       </c>
       <c r="L12" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 테이블, 지도, 버튼</t>
+          <t>텍스트, 테이블, 파일 업로드, 버튼</t>
         </is>
       </c>
       <c r="M12" s="18" t="inlineStr">
@@ -6418,7 +5914,7 @@
       </c>
       <c r="O12" s="18" t="inlineStr">
         <is>
-          <t>행 선택 시 쇼룸 상세/수정</t>
+          <t>행 선택 시 상품 상세/수정</t>
         </is>
       </c>
     </row>
@@ -6428,7 +5924,7 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>ZB-A-SHOP-01</t>
+          <t>ZB-A-SHOP-02</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -6438,7 +5934,7 @@
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>상품 관리(2차)</t>
+          <t>카테고리/브랜드 관리(2차)</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -6448,7 +5944,7 @@
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>(도출·2차) 가구 상품 등록·수정·재고·가격·노출 관리.</t>
+          <t>(도출·2차) 상품 카테고리·브랜드 마스터 관리.</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
@@ -6473,12 +5969,12 @@
       </c>
       <c r="K13" s="18" t="inlineStr">
         <is>
-          <t>목록 테이블, 입력 폼, 이미지 업로드</t>
+          <t>목록 테이블, 입력 폼</t>
         </is>
       </c>
       <c r="L13" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 테이블, 파일 업로드, 버튼</t>
+          <t>텍스트, 테이블, 버튼</t>
         </is>
       </c>
       <c r="M13" s="18" t="inlineStr">
@@ -6493,7 +5989,7 @@
       </c>
       <c r="O13" s="18" t="inlineStr">
         <is>
-          <t>행 선택 시 상품 상세/수정</t>
+          <t>행 선택 시 수정</t>
         </is>
       </c>
     </row>
@@ -6503,17 +5999,17 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>ZB-A-SHOP-02</t>
+          <t>ZB-A-ORDER-01</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>상품 관리</t>
+          <t>주문 관리</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>카테고리/브랜드 관리(2차)</t>
+          <t>주문/배송 관리(2차)</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -6523,7 +6019,7 @@
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>(도출·2차) 상품 카테고리·브랜드 마스터 관리.</t>
+          <t>(도출·2차) 주문 조회·결제 상태·배송 상태(준비중/배송중/배송완료) 관리.</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
@@ -6538,17 +6034,17 @@
       </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
           <t>CRUD</t>
         </is>
       </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
       <c r="K14" s="18" t="inlineStr">
         <is>
-          <t>목록 테이블, 입력 폼</t>
+          <t>목록 테이블, 상태 변경, 필터</t>
         </is>
       </c>
       <c r="L14" s="18" t="inlineStr">
@@ -6568,7 +6064,7 @@
       </c>
       <c r="O14" s="18" t="inlineStr">
         <is>
-          <t>행 선택 시 수정</t>
+          <t>행 선택 시 주문 상세</t>
         </is>
       </c>
     </row>
@@ -6578,17 +6074,17 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>ZB-A-ORDER-01</t>
+          <t>ZB-A-MEMBER-01</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>주문 관리</t>
+          <t>회원 관리</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>주문/배송 관리(2차)</t>
+          <t>회원 관리</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -6598,7 +6094,7 @@
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>(도출·2차) 주문 조회·결제 상태·배송 상태(준비중/배송중/배송완료) 관리.</t>
+          <t>(도출) 회원 조회·상태(정지/탈퇴)·본인인증·권한 관리.</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -6623,7 +6119,7 @@
       </c>
       <c r="K15" s="18" t="inlineStr">
         <is>
-          <t>목록 테이블, 상태 변경, 필터</t>
+          <t>목록 테이블, 검색, 상태 변경</t>
         </is>
       </c>
       <c r="L15" s="18" t="inlineStr">
@@ -6643,7 +6139,7 @@
       </c>
       <c r="O15" s="18" t="inlineStr">
         <is>
-          <t>행 선택 시 주문 상세</t>
+          <t>행 선택 시 회원 상세</t>
         </is>
       </c>
     </row>
@@ -6653,17 +6149,17 @@
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>ZB-A-MEMBER-01</t>
+          <t>ZB-A-COMM-01</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>회원 관리</t>
+          <t>커뮤니티 관리</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>회원 관리</t>
+          <t>게시글/신고 관리</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
@@ -6673,7 +6169,7 @@
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>(도출) 회원 조회·상태(정지/탈퇴)·본인인증·권한 관리.</t>
+          <t>(도출) 커뮤니티 게시글·댓글·신고 처리(숨김/삭제/제재).</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
@@ -6688,7 +6184,7 @@
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>CRUD</t>
         </is>
       </c>
       <c r="J16" s="16" t="inlineStr">
@@ -6698,7 +6194,7 @@
       </c>
       <c r="K16" s="18" t="inlineStr">
         <is>
-          <t>목록 테이블, 검색, 상태 변경</t>
+          <t>목록 테이블, 신고 큐, 처리 버튼</t>
         </is>
       </c>
       <c r="L16" s="18" t="inlineStr">
@@ -6718,7 +6214,7 @@
       </c>
       <c r="O16" s="18" t="inlineStr">
         <is>
-          <t>행 선택 시 회원 상세</t>
+          <t>행 선택 시 게시글/신고 상세</t>
         </is>
       </c>
     </row>
@@ -6728,17 +6224,17 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>ZB-A-COMM-01</t>
+          <t>ZB-A-NOTI-01</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>커뮤니티 관리</t>
+          <t>알림 관리</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>게시글/신고 관리</t>
+          <t>알림/구독 관리</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
@@ -6748,7 +6244,7 @@
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>(도출) 커뮤니티 게시글·댓글·신고 처리(숨김/삭제/제재).</t>
+          <t>(도출) 마감임박·프로모션 등 푸시/알림 발송과 구독 대상·템플릿 관리.</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
@@ -6773,17 +6269,17 @@
       </c>
       <c r="K17" s="18" t="inlineStr">
         <is>
-          <t>목록 테이블, 신고 큐, 처리 버튼</t>
+          <t>목록 테이블, 발송 폼, 대상 선택</t>
         </is>
       </c>
       <c r="L17" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 테이블, 버튼</t>
+          <t>텍스트, 입력 필드, 버튼</t>
         </is>
       </c>
       <c r="M17" s="18" t="inlineStr">
         <is>
-          <t>(없음)</t>
+          <t>발송</t>
         </is>
       </c>
       <c r="N17" s="16" t="inlineStr">
@@ -6793,7 +6289,7 @@
       </c>
       <c r="O17" s="18" t="inlineStr">
         <is>
-          <t>행 선택 시 게시글/신고 상세</t>
+          <t>발송 시 알림 큐 등록·이력 갱신</t>
         </is>
       </c>
     </row>
@@ -6803,27 +6299,27 @@
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>ZB-A-NOTI-01</t>
+          <t>ZB-A-STAT-01</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>알림 관리</t>
+          <t>통계</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>알림/구독 관리</t>
+          <t>통계 리포트</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>현황</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>(도출) 마감임박·프로모션 등 푸시/알림 발송과 구독 대상·템플릿 관리.</t>
+          <t>(도출) 청약·트래픽·커머스(2차) 지표를 기간·세그먼트별로 조회.</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr">
@@ -6838,27 +6334,27 @@
       </c>
       <c r="I18" s="17" t="inlineStr">
         <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
           <t>CRUD</t>
         </is>
       </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
       <c r="K18" s="18" t="inlineStr">
         <is>
-          <t>목록 테이블, 발송 폼, 대상 선택</t>
+          <t>차트, 필터, 다운로드</t>
         </is>
       </c>
       <c r="L18" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 입력 필드, 버튼</t>
+          <t>텍스트, 차트, 버튼</t>
         </is>
       </c>
       <c r="M18" s="18" t="inlineStr">
         <is>
-          <t>발송</t>
+          <t>(없음)</t>
         </is>
       </c>
       <c r="N18" s="16" t="inlineStr">
@@ -6868,7 +6364,7 @@
       </c>
       <c r="O18" s="18" t="inlineStr">
         <is>
-          <t>발송 시 알림 큐 등록·이력 갱신</t>
+          <t>다운로드 시 리포트 내보내기</t>
         </is>
       </c>
     </row>
@@ -6878,27 +6374,27 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>ZB-A-STAT-01</t>
+          <t>ZB-A-SYS-01</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>통계</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>통계 리포트</t>
+          <t>운영자/권한 관리</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>현황</t>
+          <t>목록</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>(도출) 청약·트래픽·커머스(2차) 지표를 기간·세그먼트별로 조회.</t>
+          <t>(도출) 운영자 계정·역할(RBAC)·권한 매핑 관리.</t>
         </is>
       </c>
       <c r="G19" s="16" t="inlineStr">
@@ -6913,7 +6409,7 @@
       </c>
       <c r="I19" s="17" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>✕</t>
         </is>
       </c>
       <c r="J19" s="16" t="inlineStr">
@@ -6923,17 +6419,17 @@
       </c>
       <c r="K19" s="18" t="inlineStr">
         <is>
-          <t>차트, 필터, 다운로드</t>
+          <t>목록 테이블, 권한 매트릭스</t>
         </is>
       </c>
       <c r="L19" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 차트, 버튼</t>
+          <t>텍스트, 테이블, 체크박스, 버튼</t>
         </is>
       </c>
       <c r="M19" s="18" t="inlineStr">
         <is>
-          <t>(없음)</t>
+          <t>저장</t>
         </is>
       </c>
       <c r="N19" s="16" t="inlineStr">
@@ -6943,7 +6439,7 @@
       </c>
       <c r="O19" s="18" t="inlineStr">
         <is>
-          <t>다운로드 시 리포트 내보내기</t>
+          <t>저장 시 권한 반영</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6449,7 @@
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>ZB-A-SYS-01</t>
+          <t>ZB-A-SYS-02</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
@@ -6963,17 +6459,17 @@
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>운영자/권한 관리</t>
+          <t>감사 로그 조회</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>목록</t>
+          <t>현황</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>(도출) 운영자 계정·역할(RBAC)·권한 매핑 관리.</t>
+          <t>(도출·검토보완) 관리자/운영자의 로그인·데이터 변경·삭제 활동 감사 로그를 조회·검색·필터한다.</t>
         </is>
       </c>
       <c r="G20" s="16" t="inlineStr">
@@ -6988,7 +6484,7 @@
       </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>R</t>
         </is>
       </c>
       <c r="J20" s="16" t="inlineStr">
@@ -6998,17 +6494,17 @@
       </c>
       <c r="K20" s="18" t="inlineStr">
         <is>
-          <t>목록 테이블, 권한 매트릭스</t>
+          <t>목록 테이블, 검색/필터</t>
         </is>
       </c>
       <c r="L20" s="18" t="inlineStr">
         <is>
-          <t>텍스트, 테이블, 체크박스, 버튼</t>
+          <t>텍스트, 테이블, 버튼</t>
         </is>
       </c>
       <c r="M20" s="18" t="inlineStr">
         <is>
-          <t>저장</t>
+          <t>(없음)</t>
         </is>
       </c>
       <c r="N20" s="16" t="inlineStr">
@@ -7018,85 +6514,11 @@
       </c>
       <c r="O20" s="18" t="inlineStr">
         <is>
-          <t>저장 시 권한 반영</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" s="19">
-      <c r="A21" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>ZB-A-SYS-02</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>시스템</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>감사 로그 조회</t>
-        </is>
-      </c>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>현황</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="inlineStr">
-        <is>
-          <t>(도출·검토보완) 관리자/운영자의 로그인·데이터 변경·삭제 활동 감사 로그를 조회·검색·필터한다.</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-      <c r="K21" s="18" t="inlineStr">
-        <is>
-          <t>목록 테이블, 검색/필터</t>
-        </is>
-      </c>
-      <c r="L21" s="18" t="inlineStr">
-        <is>
-          <t>텍스트, 테이블, 버튼</t>
-        </is>
-      </c>
-      <c r="M21" s="18" t="inlineStr">
-        <is>
-          <t>(없음)</t>
-        </is>
-      </c>
-      <c r="N21" s="16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O21" s="18" t="inlineStr">
-        <is>
           <t>행 선택 시 로그 상세</t>
         </is>
       </c>
     </row>
+    <row r="21" s="19"/>
     <row r="22" ht="15.75" customHeight="1" s="19"/>
     <row r="23" ht="15.75" customHeight="1" s="19"/>
     <row r="24" ht="15.75" customHeight="1" s="19"/>

--- a/docs/ZIPBODA_화면설계서_v0.1.xlsx
+++ b/docs/ZIPBODA_화면설계서_v0.1.xlsx
@@ -638,10 +638,24 @@
       <c r="F6" s="7" t="n"/>
     </row>
     <row r="7" ht="15.75" customHeight="1" s="20">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="9" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="7" t="n"/>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>관리자용</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Admin Figma 최신 정합(섹션 86:4294) — 9화면으로 재정합: 청약 공고 관리(목록·상세·연계 통합)·평면도/3D 자산(목록·상세 통합)·상품 &amp; 주문 관리(통합)로 축약, 청약 신청현황·쇼룸 제거 반영, 집구경(인테리어 영감), 관리자 로그인(232:80) 신규 설계 반영(미설계 해제), node-id 갱신</t>
+        </is>
+      </c>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
     </row>
@@ -12522,7 +12536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="3.75" customWidth="1" style="20" min="1" max="1"/>
@@ -12661,7 +12675,7 @@
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>관리자 로그인 [미설계]</t>
+          <t>관리자 로그인</t>
         </is>
       </c>
       <c r="E3" s="14" t="inlineStr">
@@ -12671,7 +12685,7 @@
       </c>
       <c r="F3" s="14" t="inlineStr">
         <is>
-          <t>(도출) 운영자/관리자 계정 로그인. 접근 제어·2차 인증 등 보안 정책 적용.</t>
+          <t>(도출) 관리자 콘솔 로그인 — 이메일/비밀번호, 로그인 후 2차 인증(OTP) 안내.</t>
         </is>
       </c>
       <c r="G3" s="18" t="inlineStr">
@@ -12719,9 +12733,9 @@
           <t>성공 시 관리자 대시보드</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>미설계 (Figma 부재)</t>
+      <c r="P3" s="0" t="inlineStr">
+        <is>
+          <t>232:80</t>
         </is>
       </c>
     </row>
@@ -12751,7 +12765,7 @@
       </c>
       <c r="F4" s="14" t="inlineStr">
         <is>
-          <t>(도출) 청약/회원/주문/트래픽 핵심 지표와 최근 활동·알림 요약.</t>
+          <t>(도출) KPI(활성 청약·3D 자산 업로드·활성 사용자·일일 거래액) + 청약 관심·구독·조회 트렌드·최근 활동/알림.</t>
         </is>
       </c>
       <c r="G4" s="18" t="inlineStr">
@@ -12799,9 +12813,9 @@
           <t>위젯 선택 시 상세 관리 화면</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>86:1157</t>
+      <c r="P4" s="0" t="inlineStr">
+        <is>
+          <t>86:4295</t>
         </is>
       </c>
     </row>
@@ -12821,7 +12835,7 @@
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>청약 공고 목록 관리</t>
+          <t>청약 공고 관리(목록·상세·연계)</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -12831,7 +12845,7 @@
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>(도출) 청약 공고를 검색·필터하고 상태별로 관리.</t>
+          <t>(도출) 청약 공고 등록/수정/상태·공공데이터 연계. 상세에 기관 신청 페이지 URL·주소·좌표 관리. (목록+상세 통합)</t>
         </is>
       </c>
       <c r="G5" s="18" t="inlineStr">
@@ -12879,9 +12893,9 @@
           <t>행 선택 시 공고 상세/수정, 등록 버튼 시 등록</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>86:1448</t>
+      <c r="P5" s="0" t="inlineStr">
+        <is>
+          <t>86:4296</t>
         </is>
       </c>
     </row>
@@ -12891,27 +12905,27 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>ZB-A-SUBS-02</t>
+          <t>ZB-A-PLAN-01</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>청약 관리</t>
+          <t>자산 관리</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>청약 공고 상세 관리</t>
+          <t>평면도/3D 자산 관리(목록·상세)</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>입력폼</t>
+          <t>목록</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>(도출) 청약 공고 상세 관리(단지·공급기관 LH/SH/GH/IH·일정·평형·연계 자산). 등록/수정 포함.</t>
+          <t>(도출) 공고 연계 평면도(2D)·3D(WebGL) 자산 목록·상세·업로드·매핑. (목록+상세 통합)</t>
         </is>
       </c>
       <c r="G6" s="18" t="inlineStr">
@@ -12936,17 +12950,17 @@
       </c>
       <c r="K6" s="19" t="inlineStr">
         <is>
-          <t>입력 폼, 평형 반복 입력, 파일 업로드</t>
+          <t>목록 테이블, 미리보기, 필터</t>
         </is>
       </c>
       <c r="L6" s="19" t="inlineStr">
         <is>
-          <t>텍스트, 입력 필드, 드롭다운, 버튼</t>
+          <t>텍스트, 테이블, 버튼</t>
         </is>
       </c>
       <c r="M6" s="19" t="inlineStr">
         <is>
-          <t>저장</t>
+          <t>(없음)</t>
         </is>
       </c>
       <c r="N6" s="18" t="inlineStr">
@@ -12956,12 +12970,12 @@
       </c>
       <c r="O6" s="19" t="inlineStr">
         <is>
-          <t>저장 시 목록 복귀</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>86:2911</t>
+          <t>행 선택 시 자산 상세/수정</t>
+        </is>
+      </c>
+      <c r="P6" s="0" t="inlineStr">
+        <is>
+          <t>86:4297</t>
         </is>
       </c>
     </row>
@@ -12971,17 +12985,17 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>ZB-A-PLAN-01</t>
+          <t>ZB-A-TOUR-01</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>자산 관리</t>
+          <t>콘텐츠 관리</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>평면도/3D 자산 목록</t>
+          <t>집구경(인테리어 영감) 관리</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -12991,7 +13005,7 @@
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>(도출) 평면도(2D)·3D 배치도 자산을 단지/평형별로 관리. (공고 연계)</t>
+          <t>(도출) 집구경(인테리어 영감) 콘텐츠 승인·전시·카테고리·상품 태깅 관리.</t>
         </is>
       </c>
       <c r="G7" s="18" t="inlineStr">
@@ -13006,7 +13020,7 @@
       </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>CRUD</t>
         </is>
       </c>
       <c r="J7" s="18" t="inlineStr">
@@ -13016,12 +13030,12 @@
       </c>
       <c r="K7" s="19" t="inlineStr">
         <is>
-          <t>목록 테이블, 미리보기, 필터</t>
+          <t>목록 테이블, 이미지 업로드, 태깅</t>
         </is>
       </c>
       <c r="L7" s="19" t="inlineStr">
         <is>
-          <t>텍스트, 테이블, 버튼</t>
+          <t>텍스트, 테이블, 파일 업로드, 버튼</t>
         </is>
       </c>
       <c r="M7" s="19" t="inlineStr">
@@ -13036,12 +13050,12 @@
       </c>
       <c r="O7" s="19" t="inlineStr">
         <is>
-          <t>행 선택 시 자산 상세/수정</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>86:2357</t>
+          <t>행 선택 시 콘텐츠 상세/수정</t>
+        </is>
+      </c>
+      <c r="P7" s="0" t="inlineStr">
+        <is>
+          <t>109:918</t>
         </is>
       </c>
     </row>
@@ -13051,27 +13065,27 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>ZB-A-PLAN-02</t>
+          <t>ZB-A-MEMBER-01</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>자산 관리</t>
+          <t>회원·커뮤니티 관리</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>평면도/3D 자산 상세</t>
+          <t>회원 &amp; 커뮤니티 관리</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>입력폼</t>
+          <t>목록</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>(도출) 평면도(2D)·3D(WebGL) 자산 상세·업로드·매핑 관리.</t>
+          <t>(도출) 회원과 커뮤니티(게시글·댓글·신고 처리)를 통합 관리.</t>
         </is>
       </c>
       <c r="G8" s="18" t="inlineStr">
@@ -13086,7 +13100,7 @@
       </c>
       <c r="I8" s="17" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>RU</t>
         </is>
       </c>
       <c r="J8" s="18" t="inlineStr">
@@ -13096,17 +13110,17 @@
       </c>
       <c r="K8" s="19" t="inlineStr">
         <is>
-          <t>입력 폼, 파일 업로드, 3D 미리보기</t>
+          <t>목록 테이블, 검색, 상태 변경</t>
         </is>
       </c>
       <c r="L8" s="19" t="inlineStr">
         <is>
-          <t>텍스트, 파일 업로드, 버튼</t>
+          <t>텍스트, 테이블, 버튼</t>
         </is>
       </c>
       <c r="M8" s="19" t="inlineStr">
         <is>
-          <t>저장</t>
+          <t>(없음)</t>
         </is>
       </c>
       <c r="N8" s="18" t="inlineStr">
@@ -13116,12 +13130,12 @@
       </c>
       <c r="O8" s="19" t="inlineStr">
         <is>
-          <t>저장 시 자산 목록 복귀</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>86:2712</t>
+          <t>행 선택 시 회원 상세</t>
+        </is>
+      </c>
+      <c r="P8" s="0" t="inlineStr">
+        <is>
+          <t>109:919</t>
         </is>
       </c>
     </row>
@@ -13131,17 +13145,17 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>ZB-A-TOUR-01</t>
+          <t>ZB-A-NOTI-01</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>콘텐츠 관리</t>
+          <t>알림·통계 관리</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>집구경(인테리어 영감) 관리</t>
+          <t>알림 &amp; 통계 관리</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -13151,7 +13165,7 @@
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>(도출) 집구경(인테리어 영감) 콘텐츠 등록·노출·카테고리·상품 태깅 관리.</t>
+          <t>(도출) 알림·구독 발송과 트래픽·운영 통계를 통합 관리.</t>
         </is>
       </c>
       <c r="G9" s="18" t="inlineStr">
@@ -13176,17 +13190,17 @@
       </c>
       <c r="K9" s="19" t="inlineStr">
         <is>
-          <t>목록 테이블, 이미지 업로드, 태깅</t>
+          <t>목록 테이블, 발송 폼, 대상 선택</t>
         </is>
       </c>
       <c r="L9" s="19" t="inlineStr">
         <is>
-          <t>텍스트, 테이블, 파일 업로드, 버튼</t>
+          <t>텍스트, 입력 필드, 버튼</t>
         </is>
       </c>
       <c r="M9" s="19" t="inlineStr">
         <is>
-          <t>(없음)</t>
+          <t>발송</t>
         </is>
       </c>
       <c r="N9" s="18" t="inlineStr">
@@ -13196,12 +13210,12 @@
       </c>
       <c r="O9" s="19" t="inlineStr">
         <is>
-          <t>행 선택 시 콘텐츠 상세/수정</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>109:63</t>
+          <t>발송 시 알림 큐 등록·이력 갱신</t>
+        </is>
+      </c>
+      <c r="P9" s="0" t="inlineStr">
+        <is>
+          <t>109:920</t>
         </is>
       </c>
     </row>
@@ -13211,17 +13225,17 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>ZB-A-MEMBER-01</t>
+          <t>ZB-A-SHOP-01</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>회원·커뮤니티 관리</t>
+          <t>상품·주문 관리</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>회원 &amp; 커뮤니티 관리</t>
+          <t>상품 &amp; 주문 관리</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -13231,7 +13245,7 @@
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>(도출) 회원과 커뮤니티(게시글·댓글·신고 처리)를 통합 관리.</t>
+          <t>(도출·2차) 가구 상품·재고·카테고리와 주문·배송을 통합 관리.</t>
         </is>
       </c>
       <c r="G10" s="18" t="inlineStr">
@@ -13246,7 +13260,7 @@
       </c>
       <c r="I10" s="17" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>CRUD</t>
         </is>
       </c>
       <c r="J10" s="18" t="inlineStr">
@@ -13256,12 +13270,12 @@
       </c>
       <c r="K10" s="19" t="inlineStr">
         <is>
-          <t>목록 테이블, 검색, 상태 변경</t>
+          <t>목록 테이블, 입력 폼, 이미지 업로드</t>
         </is>
       </c>
       <c r="L10" s="19" t="inlineStr">
         <is>
-          <t>텍스트, 테이블, 버튼</t>
+          <t>텍스트, 테이블, 파일 업로드, 버튼</t>
         </is>
       </c>
       <c r="M10" s="19" t="inlineStr">
@@ -13276,12 +13290,12 @@
       </c>
       <c r="O10" s="19" t="inlineStr">
         <is>
-          <t>행 선택 시 회원 상세</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>109:342</t>
+          <t>행 선택 시 상품 상세/수정</t>
+        </is>
+      </c>
+      <c r="P10" s="0" t="inlineStr">
+        <is>
+          <t>86:4298</t>
         </is>
       </c>
     </row>
@@ -13291,17 +13305,17 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>ZB-A-NOTI-01</t>
+          <t>ZB-A-SYS-01</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>알림·통계 관리</t>
+          <t>시스템</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>알림 &amp; 통계 관리</t>
+          <t>시스템 &amp; 감사로그</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -13311,7 +13325,7 @@
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>(도출) 알림·구독 발송과 운영 통계 지표를 통합 관리.</t>
+          <t>(도출) 운영자·권한(RBAC)과 감사 로그를 통합 관리.</t>
         </is>
       </c>
       <c r="G11" s="18" t="inlineStr">
@@ -13326,27 +13340,27 @@
       </c>
       <c r="I11" s="17" t="inlineStr">
         <is>
+          <t>✕</t>
+        </is>
+      </c>
+      <c r="J11" s="18" t="inlineStr">
+        <is>
           <t>CRUD</t>
         </is>
       </c>
-      <c r="J11" s="18" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
       <c r="K11" s="19" t="inlineStr">
         <is>
-          <t>목록 테이블, 발송 폼, 대상 선택</t>
+          <t>목록 테이블, 권한 매트릭스</t>
         </is>
       </c>
       <c r="L11" s="19" t="inlineStr">
         <is>
-          <t>텍스트, 입력 필드, 버튼</t>
+          <t>텍스트, 테이블, 체크박스, 버튼</t>
         </is>
       </c>
       <c r="M11" s="19" t="inlineStr">
         <is>
-          <t>발송</t>
+          <t>저장</t>
         </is>
       </c>
       <c r="N11" s="18" t="inlineStr">
@@ -13356,252 +13370,12 @@
       </c>
       <c r="O11" s="19" t="inlineStr">
         <is>
-          <t>발송 시 알림 큐 등록·이력 갱신</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>109:650</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>ZB-A-SHOP-01</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>상품 관리</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>상품 관리(카테고리/브랜드 포함)</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>목록</t>
-        </is>
-      </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>(도출·2차) 가구 상품·카테고리·브랜드·재고·가격·노출 통합 관리.</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="H12" s="18" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-      <c r="J12" s="18" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-      <c r="K12" s="19" t="inlineStr">
-        <is>
-          <t>목록 테이블, 입력 폼, 이미지 업로드</t>
-        </is>
-      </c>
-      <c r="L12" s="19" t="inlineStr">
-        <is>
-          <t>텍스트, 테이블, 파일 업로드, 버튼</t>
-        </is>
-      </c>
-      <c r="M12" s="19" t="inlineStr">
-        <is>
-          <t>(없음)</t>
-        </is>
-      </c>
-      <c r="N12" s="18" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O12" s="19" t="inlineStr">
-        <is>
-          <t>행 선택 시 상품 상세/수정</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>86:3346</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>ZB-A-ORDER-01</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>주문 관리</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>주문/배송 관리(2차)</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>목록</t>
-        </is>
-      </c>
-      <c r="F13" s="14" t="inlineStr">
-        <is>
-          <t>(도출·2차) 주문 조회·결제 상태·배송 상태(준비중/배송중/배송완료) 관리.</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>RU</t>
-        </is>
-      </c>
-      <c r="J13" s="18" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-      <c r="K13" s="19" t="inlineStr">
-        <is>
-          <t>목록 테이블, 상태 변경, 필터</t>
-        </is>
-      </c>
-      <c r="L13" s="19" t="inlineStr">
-        <is>
-          <t>텍스트, 테이블, 버튼</t>
-        </is>
-      </c>
-      <c r="M13" s="19" t="inlineStr">
-        <is>
-          <t>(없음)</t>
-        </is>
-      </c>
-      <c r="N13" s="18" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O13" s="19" t="inlineStr">
-        <is>
-          <t>행 선택 시 주문 상세</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>86:3758</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>ZB-A-SYS-01</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>시스템 관리</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>시스템 &amp; 감사로그</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="inlineStr">
-        <is>
-          <t>목록</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>(도출) 운영자·권한(RBAC)과 감사 로그를 통합 관리.</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>✕</t>
-        </is>
-      </c>
-      <c r="J14" s="18" t="inlineStr">
-        <is>
-          <t>CRUD</t>
-        </is>
-      </c>
-      <c r="K14" s="19" t="inlineStr">
-        <is>
-          <t>목록 테이블, 권한 매트릭스</t>
-        </is>
-      </c>
-      <c r="L14" s="19" t="inlineStr">
-        <is>
-          <t>텍스트, 테이블, 체크박스, 버튼</t>
-        </is>
-      </c>
-      <c r="M14" s="19" t="inlineStr">
-        <is>
-          <t>저장</t>
-        </is>
-      </c>
-      <c r="N14" s="18" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O14" s="19" t="inlineStr">
-        <is>
           <t>저장 시 권한 반영</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>86:1784</t>
+      <c r="P11" s="0" t="inlineStr">
+        <is>
+          <t>86:4299</t>
         </is>
       </c>
     </row>

--- a/docs/ZIPBODA_화면설계서_v0.1.xlsx
+++ b/docs/ZIPBODA_화면설계서_v0.1.xlsx
@@ -15,8 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -485,7 +486,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1000"/>
+  <dimension ref="A1:F1001"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="3.88" customWidth="1" style="20" min="1" max="1"/>
@@ -660,10 +661,24 @@
       <c r="F7" s="7" t="n"/>
     </row>
     <row r="8" ht="15.75" customHeight="1" s="20">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>사용자용</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>마이페이지 라우팅 정합 — 나의 청약(MY-01)·찜 목록(MY-02)·주문내역(MY-03)을 단일 /my 페이지 내 탭 전환으로 구현 정합(별도 URL 미사용). 프로필 수정(MY-04)은 /my/profile 별도 유지. 화면ID·node-id 유지.</t>
+        </is>
+      </c>
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
     </row>
@@ -8602,6 +8617,14 @@
       <c r="D1000" s="12" t="n"/>
       <c r="E1000" s="12" t="n"/>
       <c r="F1000" s="12" t="n"/>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="12" t="n"/>
+      <c r="B1001" s="12" t="n"/>
+      <c r="C1001" s="12" t="n"/>
+      <c r="D1001" s="12" t="n"/>
+      <c r="E1001" s="12" t="n"/>
+      <c r="F1001" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
@@ -10664,7 +10687,7 @@
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>(공통) 프로필(인증 상태)·통계와 관심/구독 공고 목록(단지·상태·D-day). 각 공고에서 기관 신청 바로가기와 '신청함' 자가표시 관리.</t>
+          <t>(공통) 프로필(인증 상태)·통계와 관심/구독 공고 목록(단지·상태·D-day). 각 공고에서 기관 신청 바로가기와 '신청함' 자가표시 관리. (마이페이지 /my 단일 페이지 내 '나의 청약' 탭으로 제공)</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
@@ -10754,7 +10777,7 @@
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>(공통·2차) 찜한 가구 목록(브랜드·상품명·가격)과 '구매'·'삭제'.</t>
+          <t>(공통·2차) 찜한 가구 목록(브랜드·상품명·가격)과 '구매'·'삭제'. (마이페이지 /my 단일 페이지 내 '찜 목록' 탭으로 제공)</t>
         </is>
       </c>
       <c r="G25" s="17" t="inlineStr">
@@ -10844,7 +10867,7 @@
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>(공통·2차) 주문 목록과 배송 상태 뱃지(배송완료/배송중/준비중).</t>
+          <t>(공통·2차) 주문 목록과 배송 상태 뱃지(배송완료/배송중/준비중). (마이페이지 /my 단일 페이지 내 '주문내역' 탭으로 제공)</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr">

--- a/docs/ZIPBODA_화면설계서_v0.1.xlsx
+++ b/docs/ZIPBODA_화면설계서_v0.1.xlsx
@@ -683,10 +683,24 @@
       <c r="F8" s="7" t="n"/>
     </row>
     <row r="9" ht="15.75" customHeight="1" s="20">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>46238</v>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>사용자용</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>집구경(TOUR-01/02) PC 지원 반영 — Figma PC 노드(135:2921 갤러리·135:3135 라이트박스) 확인·구현, PC ✕→O·node-id 추가. 구현이 Figma PC 대비 의도적 개선분 있어 편차 기록(Figma 갱신 예정).</t>
+        </is>
+      </c>
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="7" t="n"/>
     </row>
@@ -9697,7 +9711,7 @@
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>(공통) '인테리어 영감' 갤러리. 공간 카테고리(전체/거실/침실/주방/다이닝/서재/욕실) 탭 + 실제 유저 홈 사진 그리드(@핸들·❤️ 좋아요).</t>
+          <t>(공통) '인테리어 영감' 갤러리. 공간 카테고리(전체/거실/침실/주방/다이닝/서재/욕실) 탭 + 실제 유저 홈 사진 그리드(@핸들·❤️ 좋아요). (PC 지원 반영 — 갤러리. 구현이 Figma PC와 일부 상이한 의도적 개선분 있음, Figma 갱신 예정)</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
@@ -9747,7 +9761,7 @@
       </c>
       <c r="P13" s="0" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>O</t>
         </is>
       </c>
       <c r="Q13" s="0" t="inlineStr">
@@ -9757,7 +9771,7 @@
       </c>
       <c r="R13" s="0" t="inlineStr">
         <is>
-          <t>— / 1:1851</t>
+          <t>135:2921 / 1:1851</t>
         </is>
       </c>
     </row>
@@ -9787,7 +9801,7 @@
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>(공통) 인테리어 사진 상세(작성자·좋아요)와 '이 스타일 쇼핑하기'로 사진 속 가구 쇼핑 유도.</t>
+          <t>(공통) 인테리어 사진 상세(작성자·좋아요)와 '이 스타일 쇼핑하기'로 사진 속 가구 쇼핑 유도. (PC는 갤러리 내 라이트박스로 구현. Figma PC 대비 개선분 있음, Figma 갱신 예정)</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
@@ -9837,7 +9851,7 @@
       </c>
       <c r="P14" s="0" t="inlineStr">
         <is>
-          <t>✕</t>
+          <t>O</t>
         </is>
       </c>
       <c r="Q14" s="0" t="inlineStr">
@@ -9847,7 +9861,7 @@
       </c>
       <c r="R14" s="0" t="inlineStr">
         <is>
-          <t>— / 1:1976</t>
+          <t>135:3135 / 1:1976</t>
         </is>
       </c>
     </row>
